--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2475,6 +2475,312 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121558110</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90737</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>734701</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7130043</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121558111</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56559</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>734673</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7130046</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121558113</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97142</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Botrychium multifidum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(S. G. Gmel.) Rupr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>734460</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7130047</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -2477,10 +2477,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121558110</v>
+        <v>121558113</v>
       </c>
       <c r="B17" t="n">
-        <v>90737</v>
+        <v>97143</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>167</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734701</v>
+        <v>734460</v>
       </c>
       <c r="R17" t="n">
-        <v>7130043</v>
+        <v>7130047</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121558111</v>
+        <v>121558110</v>
       </c>
       <c r="B18" t="n">
-        <v>56559</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734673</v>
+        <v>734701</v>
       </c>
       <c r="R18" t="n">
-        <v>7130046</v>
+        <v>7130043</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121558113</v>
+        <v>121558111</v>
       </c>
       <c r="B19" t="n">
-        <v>97142</v>
+        <v>56560</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>167</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734460</v>
+        <v>734673</v>
       </c>
       <c r="R19" t="n">
-        <v>7130047</v>
+        <v>7130046</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -2579,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121558110</v>
+        <v>121558111</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>56560</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734701</v>
+        <v>734673</v>
       </c>
       <c r="R18" t="n">
-        <v>7130043</v>
+        <v>7130046</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121558111</v>
+        <v>121558110</v>
       </c>
       <c r="B19" t="n">
-        <v>56560</v>
+        <v>90738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734673</v>
+        <v>734701</v>
       </c>
       <c r="R19" t="n">
-        <v>7130046</v>
+        <v>7130043</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -2477,10 +2477,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121558113</v>
+        <v>121558110</v>
       </c>
       <c r="B17" t="n">
-        <v>97143</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>167</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734460</v>
+        <v>734701</v>
       </c>
       <c r="R17" t="n">
-        <v>7130047</v>
+        <v>7130043</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121558111</v>
+        <v>121558113</v>
       </c>
       <c r="B18" t="n">
-        <v>56560</v>
+        <v>97143</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>167</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734673</v>
+        <v>734460</v>
       </c>
       <c r="R18" t="n">
-        <v>7130046</v>
+        <v>7130047</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121558110</v>
+        <v>121558111</v>
       </c>
       <c r="B19" t="n">
-        <v>90738</v>
+        <v>56560</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734701</v>
+        <v>734673</v>
       </c>
       <c r="R19" t="n">
-        <v>7130043</v>
+        <v>7130046</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -2572,17 +2572,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121558113</v>
+        <v>121558111</v>
       </c>
       <c r="B18" t="n">
-        <v>97143</v>
+        <v>56560</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>167</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734460</v>
+        <v>734673</v>
       </c>
       <c r="R18" t="n">
-        <v>7130047</v>
+        <v>7130046</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2674,17 +2674,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121558111</v>
+        <v>121558113</v>
       </c>
       <c r="B19" t="n">
-        <v>56560</v>
+        <v>97143</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>167</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734673</v>
+        <v>734460</v>
       </c>
       <c r="R19" t="n">
-        <v>7130046</v>
+        <v>7130047</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Jesper Wadstein, Linda Johannesson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -2477,10 +2477,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121558110</v>
+        <v>121558113</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>97151</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>167</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734701</v>
+        <v>734460</v>
       </c>
       <c r="R17" t="n">
-        <v>7130043</v>
+        <v>7130047</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2572,17 +2572,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121558111</v>
+        <v>121558110</v>
       </c>
       <c r="B18" t="n">
-        <v>56560</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734673</v>
+        <v>734701</v>
       </c>
       <c r="R18" t="n">
-        <v>7130046</v>
+        <v>7130043</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2674,17 +2674,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121558113</v>
+        <v>121558111</v>
       </c>
       <c r="B19" t="n">
-        <v>97143</v>
+        <v>56561</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>167</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734460</v>
+        <v>734673</v>
       </c>
       <c r="R19" t="n">
-        <v>7130047</v>
+        <v>7130046</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jesper Wadstein, Linda Johannesson</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -2477,10 +2477,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121558113</v>
+        <v>121558111</v>
       </c>
       <c r="B17" t="n">
-        <v>97151</v>
+        <v>56561</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>167</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Höstlåsbräken</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Botrychium multifidum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Rupr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734460</v>
+        <v>734673</v>
       </c>
       <c r="R17" t="n">
-        <v>7130047</v>
+        <v>7130046</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121558110</v>
+        <v>121558113</v>
       </c>
       <c r="B18" t="n">
-        <v>90746</v>
+        <v>97151</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>167</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>734701</v>
+        <v>734460</v>
       </c>
       <c r="R18" t="n">
-        <v>7130043</v>
+        <v>7130047</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121558111</v>
+        <v>121558110</v>
       </c>
       <c r="B19" t="n">
-        <v>56561</v>
+        <v>90746</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734673</v>
+        <v>734701</v>
       </c>
       <c r="R19" t="n">
-        <v>7130046</v>
+        <v>7130043</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -2477,10 +2477,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121558111</v>
+        <v>121558110</v>
       </c>
       <c r="B17" t="n">
-        <v>56561</v>
+        <v>90746</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>734673</v>
+        <v>734701</v>
       </c>
       <c r="R17" t="n">
-        <v>7130046</v>
+        <v>7130043</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121558110</v>
+        <v>121558111</v>
       </c>
       <c r="B19" t="n">
-        <v>90746</v>
+        <v>56561</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,21 +2697,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>734701</v>
+        <v>734673</v>
       </c>
       <c r="R19" t="n">
-        <v>7130043</v>
+        <v>7130046</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -2786,7 +2786,7 @@
         <v>122037400</v>
       </c>
       <c r="B20" t="n">
-        <v>90161</v>
+        <v>90171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -2786,7 +2786,7 @@
         <v>122037400</v>
       </c>
       <c r="B20" t="n">
-        <v>90171</v>
+        <v>90183</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -2786,7 +2786,7 @@
         <v>122037400</v>
       </c>
       <c r="B20" t="n">
-        <v>90183</v>
+        <v>90187</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2883,6 +2883,3201 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126471151</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>734710</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7130064</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126471140</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>734489</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7130009</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126471146</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97245</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>734511</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7129989</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126471135</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>734442</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7130104</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126471139</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>734476</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7130034</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126453315</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>734521</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7130071</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126471142</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>734381</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7130059</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126471143</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>734485</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7130075</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126471141</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>734399</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7130020</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126471138</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>734551</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7130083</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126471136</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>734726</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7130095</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126471137</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>734698</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7130038</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126471149</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58334</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>734456</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7130041</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126450174</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Åhedbäcken, Åhedbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>734460</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7130034</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126450989</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>734482</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7130018</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126471144</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>734468</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7130016</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126454050</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Krycklans naturreservat, Vindeln, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>734556</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7130094</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126450252</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>734492</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7130023</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126471152</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>734559</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7130073</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126471145</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>734384</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7130056</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126453484</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Krycklans naturreservat, Vindeln, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>734560</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7130067</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126450641</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>734475</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7129990</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126454548</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Krycklans naturreservat, Vindeln, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>734659</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7130059</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosök, hackhål</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126458119</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Krycklans naturreservat, Vindeln, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>734581</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7130043</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Födosök, hackhål</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126458027</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>734643</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7130074</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126471133</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91210</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>734438</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7130091</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126458220</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Åhedbäcken, Åhedbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>734479</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7130087</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126451071</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>734480</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7130023</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126452836</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Åhedbäcken, Åhedbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>734480</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7130075</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Amanda Portström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126471147</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78739</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>734647</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7130075</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126471154</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91263</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Krycklan, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>734417</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7130047</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -3083,32 +3083,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126471146</v>
+        <v>126471135</v>
       </c>
       <c r="B23" t="n">
-        <v>97245</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>734511</v>
+        <v>734442</v>
       </c>
       <c r="R23" t="n">
-        <v>7129989</v>
+        <v>7130104</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3180,32 +3180,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126471135</v>
+        <v>126471146</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>97245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>734442</v>
+        <v>734511</v>
       </c>
       <c r="R24" t="n">
-        <v>7130104</v>
+        <v>7129989</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126471142</v>
+        <v>126471141</v>
       </c>
       <c r="B27" t="n">
         <v>57657</v>
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>734381</v>
+        <v>734399</v>
       </c>
       <c r="R27" t="n">
-        <v>7130059</v>
+        <v>7130020</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126471143</v>
+        <v>126471142</v>
       </c>
       <c r="B28" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3594,16 +3594,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3612,20 +3612,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>734485</v>
+        <v>734381</v>
       </c>
       <c r="R28" t="n">
-        <v>7130075</v>
+        <v>7130059</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3684,10 +3680,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126471141</v>
+        <v>126471143</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3695,16 +3691,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3713,16 +3709,20 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>734399</v>
+        <v>734485</v>
       </c>
       <c r="R29" t="n">
-        <v>7130020</v>
+        <v>7130075</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3975,10 +3975,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126471137</v>
+        <v>126450989</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3986,37 +3986,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Krycklan, Vb</t>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>734698</v>
+        <v>734482</v>
       </c>
       <c r="R32" t="n">
-        <v>7130038</v>
+        <v>7130018</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4043,9 +4043,19 @@
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4060,60 +4070,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126471149</v>
+        <v>126450174</v>
       </c>
       <c r="B33" t="n">
-        <v>58334</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103044</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Krycklan, Vb</t>
+          <t>Åhedbäcken, Åhedbäcken, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>734456</v>
+        <v>734460</v>
       </c>
       <c r="R33" t="n">
-        <v>7130041</v>
+        <v>7130034</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4140,9 +4150,19 @@
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4157,22 +4177,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126450174</v>
+        <v>126471137</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4180,37 +4200,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åhedbäcken, Åhedbäcken, Vb</t>
+          <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>734460</v>
+        <v>734698</v>
       </c>
       <c r="R34" t="n">
-        <v>7130034</v>
+        <v>7130038</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4237,19 +4257,9 @@
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,60 +4274,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126450989</v>
+        <v>126471149</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>58334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+          <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>734482</v>
+        <v>734456</v>
       </c>
       <c r="R35" t="n">
-        <v>7130018</v>
+        <v>7130041</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4344,19 +4354,9 @@
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4371,12 +4371,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126454050</v>
+        <v>126471152</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4495,37 +4495,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Vindeln, Vb</t>
+          <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>734556</v>
+        <v>734559</v>
       </c>
       <c r="R37" t="n">
-        <v>7130094</v>
+        <v>7130073</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4552,44 +4555,30 @@
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4703,10 +4692,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126471152</v>
+        <v>126454050</v>
       </c>
       <c r="B39" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4714,40 +4703,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Krycklan, Vb</t>
+          <t>Krycklans naturreservat, Vindeln, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>734559</v>
+        <v>734556</v>
       </c>
       <c r="R39" t="n">
-        <v>7130073</v>
+        <v>7130094</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4774,40 +4760,54 @@
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126471145</v>
+        <v>126453484</v>
       </c>
       <c r="B40" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4815,16 +4815,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4833,23 +4833,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Krycklan, Vb</t>
+          <t>Krycklans naturreservat, Vindeln, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>734384</v>
+        <v>734560</v>
       </c>
       <c r="R40" t="n">
-        <v>7130056</v>
+        <v>7130067</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4876,9 +4872,24 @@
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4893,22 +4904,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126453484</v>
+        <v>126471145</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4916,16 +4927,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4934,19 +4945,23 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Vindeln, Vb</t>
+          <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>734560</v>
+        <v>734384</v>
       </c>
       <c r="R41" t="n">
-        <v>7130067</v>
+        <v>7130056</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4973,24 +4988,9 @@
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5005,22 +5005,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126450641</v>
+        <v>126454548</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5028,34 +5028,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+          <t>Krycklans naturreservat, Vindeln, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>734475</v>
+        <v>734659</v>
       </c>
       <c r="R42" t="n">
-        <v>7129990</v>
+        <v>7130059</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,7 +5091,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5097,7 +5101,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosök, hackhål</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5124,10 +5133,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126454548</v>
+        <v>126450641</v>
       </c>
       <c r="B43" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5135,38 +5144,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Vindeln, Vb</t>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>734659</v>
+        <v>734475</v>
       </c>
       <c r="R43" t="n">
-        <v>7130059</v>
+        <v>7129990</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5198,7 +5203,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5208,12 +5213,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosök, hackhål</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5556,7 +5556,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126458220</v>
+        <v>126451071</v>
       </c>
       <c r="B47" t="n">
         <v>78980</v>
@@ -5585,16 +5585,21 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Åhedbäcken, Åhedbäcken, Vb</t>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>734479</v>
+        <v>734480</v>
       </c>
       <c r="R47" t="n">
-        <v>7130087</v>
+        <v>7130023</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5626,7 +5631,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5636,7 +5641,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5663,7 +5668,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126451071</v>
+        <v>126458220</v>
       </c>
       <c r="B48" t="n">
         <v>78980</v>
@@ -5692,21 +5697,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+          <t>Åhedbäcken, Åhedbäcken, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>734480</v>
+        <v>734479</v>
       </c>
       <c r="R48" t="n">
-        <v>7130023</v>
+        <v>7130087</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5775,10 +5775,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126452836</v>
+        <v>126471147</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5786,37 +5786,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Åhedbäcken, Åhedbäcken, Vb</t>
+          <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>734480</v>
+        <v>734647</v>
       </c>
       <c r="R49" t="n">
         <v>7130075</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5843,19 +5843,9 @@
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5870,22 +5860,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126471147</v>
+        <v>126471154</v>
       </c>
       <c r="B50" t="n">
-        <v>78739</v>
+        <v>91263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5893,34 +5883,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>734647</v>
+        <v>734417</v>
       </c>
       <c r="R50" t="n">
-        <v>7130075</v>
+        <v>7130047</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5961,6 +5954,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5979,10 +5973,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126471154</v>
+        <v>126452836</v>
       </c>
       <c r="B51" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5990,40 +5984,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Krycklan, Vb</t>
+          <t>Åhedbäcken, Åhedbäcken, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>734417</v>
+        <v>734480</v>
       </c>
       <c r="R51" t="n">
-        <v>7130047</v>
+        <v>7130075</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6050,30 +6041,39 @@
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -5775,10 +5775,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126471147</v>
+        <v>126471154</v>
       </c>
       <c r="B49" t="n">
-        <v>78739</v>
+        <v>91263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5786,34 +5786,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>734647</v>
+        <v>734417</v>
       </c>
       <c r="R49" t="n">
-        <v>7130075</v>
+        <v>7130047</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5854,6 +5857,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5872,10 +5876,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126471154</v>
+        <v>126452836</v>
       </c>
       <c r="B50" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5883,40 +5887,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Krycklan, Vb</t>
+          <t>Åhedbäcken, Åhedbäcken, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>734417</v>
+        <v>734480</v>
       </c>
       <c r="R50" t="n">
-        <v>7130047</v>
+        <v>7130075</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5943,40 +5944,49 @@
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126452836</v>
+        <v>126471147</v>
       </c>
       <c r="B51" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5984,37 +5994,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Åhedbäcken, Åhedbäcken, Vb</t>
+          <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>734480</v>
+        <v>734647</v>
       </c>
       <c r="R51" t="n">
         <v>7130075</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6041,19 +6051,9 @@
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6068,12 +6068,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -3486,10 +3486,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126471141</v>
+        <v>126471143</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3497,16 +3497,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3515,16 +3515,20 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>734399</v>
+        <v>734485</v>
       </c>
       <c r="R27" t="n">
-        <v>7130020</v>
+        <v>7130075</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3583,7 +3587,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126471142</v>
+        <v>126471141</v>
       </c>
       <c r="B28" t="n">
         <v>57657</v>
@@ -3618,10 +3622,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>734381</v>
+        <v>734399</v>
       </c>
       <c r="R28" t="n">
-        <v>7130059</v>
+        <v>7130020</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3680,10 +3684,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126471143</v>
+        <v>126471142</v>
       </c>
       <c r="B29" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3691,16 +3695,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3709,20 +3713,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>734485</v>
+        <v>734381</v>
       </c>
       <c r="R29" t="n">
-        <v>7130075</v>
+        <v>7130059</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126450989</v>
+        <v>126450174</v>
       </c>
       <c r="B32" t="n">
         <v>78980</v>
@@ -4006,14 +4006,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+          <t>Åhedbäcken, Åhedbäcken, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>734482</v>
+        <v>734460</v>
       </c>
       <c r="R32" t="n">
-        <v>7130018</v>
+        <v>7130034</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4082,7 +4082,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126450174</v>
+        <v>126450989</v>
       </c>
       <c r="B33" t="n">
         <v>78980</v>
@@ -4113,14 +4113,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Åhedbäcken, Åhedbäcken, Vb</t>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>734460</v>
+        <v>734482</v>
       </c>
       <c r="R33" t="n">
-        <v>7130034</v>
+        <v>7130018</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5017,10 +5017,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126454548</v>
+        <v>126450641</v>
       </c>
       <c r="B42" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5028,38 +5028,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Vindeln, Vb</t>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>734659</v>
+        <v>734475</v>
       </c>
       <c r="R42" t="n">
-        <v>7130059</v>
+        <v>7129990</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5091,7 +5087,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5101,12 +5097,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosök, hackhål</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5133,10 +5124,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126450641</v>
+        <v>126454548</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5144,34 +5135,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+          <t>Krycklans naturreservat, Vindeln, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>734475</v>
+        <v>734659</v>
       </c>
       <c r="R43" t="n">
-        <v>7129990</v>
+        <v>7130059</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5203,7 +5198,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5213,7 +5208,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosök, hackhål</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5556,7 +5556,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126451071</v>
+        <v>126458220</v>
       </c>
       <c r="B47" t="n">
         <v>78980</v>
@@ -5585,21 +5585,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+          <t>Åhedbäcken, Åhedbäcken, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>734480</v>
+        <v>734479</v>
       </c>
       <c r="R47" t="n">
-        <v>7130023</v>
+        <v>7130087</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5631,7 +5626,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5641,7 +5636,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5668,7 +5663,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126458220</v>
+        <v>126451071</v>
       </c>
       <c r="B48" t="n">
         <v>78980</v>
@@ -5697,16 +5692,21 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Åhedbäcken, Åhedbäcken, Vb</t>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>734479</v>
+        <v>734480</v>
       </c>
       <c r="R48" t="n">
-        <v>7130087</v>
+        <v>7130023</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5775,10 +5775,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126471154</v>
+        <v>126452836</v>
       </c>
       <c r="B49" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5786,40 +5786,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Krycklan, Vb</t>
+          <t>Åhedbäcken, Åhedbäcken, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>734417</v>
+        <v>734480</v>
       </c>
       <c r="R49" t="n">
-        <v>7130047</v>
+        <v>7130075</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5846,40 +5843,49 @@
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126452836</v>
+        <v>126471154</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>91263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5887,37 +5893,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Åhedbäcken, Åhedbäcken, Vb</t>
+          <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>734480</v>
+        <v>734417</v>
       </c>
       <c r="R50" t="n">
-        <v>7130075</v>
+        <v>7130047</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5944,39 +5953,30 @@
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126471152</v>
+        <v>126454050</v>
       </c>
       <c r="B37" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4495,40 +4495,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Krycklan, Vb</t>
+          <t>Krycklans naturreservat, Vindeln, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>734559</v>
+        <v>734556</v>
       </c>
       <c r="R37" t="n">
-        <v>7130073</v>
+        <v>7130094</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4555,40 +4552,54 @@
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126450252</v>
+        <v>126471152</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>91263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4596,37 +4607,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+          <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>734492</v>
+        <v>734559</v>
       </c>
       <c r="R38" t="n">
-        <v>7130023</v>
+        <v>7130073</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4653,49 +4667,40 @@
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126454050</v>
+        <v>126450252</v>
       </c>
       <c r="B39" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4703,34 +4708,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Vindeln, Vb</t>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>734556</v>
+        <v>734492</v>
       </c>
       <c r="R39" t="n">
-        <v>7130094</v>
+        <v>7130023</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4762,7 +4767,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4772,12 +4777,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 12302-2021 artfynd.xlsx
+++ b/artfynd/A 12302-2021 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126454050</v>
+        <v>126471152</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4495,37 +4495,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Vindeln, Vb</t>
+          <t>Krycklan, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>734556</v>
+        <v>734559</v>
       </c>
       <c r="R37" t="n">
-        <v>7130094</v>
+        <v>7130073</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4552,54 +4555,40 @@
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Amanda Portström</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126471152</v>
+        <v>126450252</v>
       </c>
       <c r="B38" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,40 +4596,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Krycklan, Vb</t>
+          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>734559</v>
+        <v>734492</v>
       </c>
       <c r="R38" t="n">
-        <v>7130073</v>
+        <v>7130023</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4667,40 +4653,49 @@
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-06</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Amanda Portström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126450252</v>
+        <v>126454050</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4708,34 +4703,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Krycklans naturreservat, Krycklans naturreservat, Vb</t>
+          <t>Krycklans naturreservat, Vindeln, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>734492</v>
+        <v>734556</v>
       </c>
       <c r="R39" t="n">
-        <v>7130023</v>
+        <v>7130094</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4767,7 +4762,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4777,7 +4772,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
